--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,61 +794,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136870720</v>
+        <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58872</v>
+        <v>58167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Alkärr, Sk</t>
+          <t>Risebergagården skogsbetesmark, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>396999</v>
+        <v>396980</v>
       </c>
       <c r="R3" t="n">
-        <v>6214170</v>
+        <v>6214169</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,9 +862,19 @@
           <t>2026-09-25</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,7 +900,240 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137150290</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136870720</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58872</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alkärr, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>396999</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6214170</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136870720</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137150293</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risebergagården skogsbetesmark, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>396992</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6214178</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Årsunge</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150293</t>
         </is>
       </c>
     </row>
@@ -912,6 +1141,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870694</v>
       </c>
       <c r="B2" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136870720</v>
       </c>
       <c r="B4" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137150293</v>
       </c>
       <c r="B5" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870694</v>
       </c>
       <c r="B2" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58180</v>
+        <v>58182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136870720</v>
       </c>
       <c r="B4" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137150293</v>
       </c>
       <c r="B5" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -940,11 +936,7 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870694</v>
       </c>
       <c r="B2" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58182</v>
+        <v>58192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136870720</v>
       </c>
       <c r="B4" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137150293</v>
       </c>
       <c r="B5" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870694</v>
       </c>
       <c r="B2" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58192</v>
+        <v>58193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136870720</v>
       </c>
       <c r="B4" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137150293</v>
       </c>
       <c r="B5" t="n">
-        <v>58897</v>
+        <v>58899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136870694</v>
       </c>
       <c r="B2" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58193</v>
+        <v>58194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136870720</v>
       </c>
       <c r="B4" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137150293</v>
       </c>
       <c r="B5" t="n">
-        <v>58899</v>
+        <v>58903</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39440-2026 artfynd.xlsx
+++ b/artfynd/A 39440-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137150290</v>
       </c>
       <c r="B3" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137150293</v>
       </c>
       <c r="B5" t="n">
-        <v>58903</v>
+        <v>58906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
